--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488034_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488034_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0962</v>
+        <v>3.6731</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5373</v>
+        <v>4.2546</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4411</v>
+        <v>-0.5815</v>
       </c>
       <c r="G2" t="n">
         <v>1.7166</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8373</v>
+        <v>1.4142</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2997</v>
+        <v>1.017</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5376</v>
+        <v>0.3972</v>
       </c>
       <c r="V2" t="n">
         <v>0.1459</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5902</v>
+        <v>2.7254</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3114</v>
+        <v>3.3343</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7212</v>
+        <v>-0.6089</v>
       </c>
       <c r="G3" t="n">
         <v>0.2232</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0477</v>
+        <v>1.183</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3709</v>
+        <v>0.3939</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6768</v>
+        <v>0.7891</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3055</v>
+        <v>1.6799</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2879</v>
+        <v>1.1622</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0176</v>
+        <v>0.5177</v>
       </c>
       <c r="G4" t="n">
-        <v>0.305</v>
+        <v>0.8374</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6246</v>
+        <v>0.409</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3196</v>
+        <v>0.4285</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9417</v>
+        <v>1.3558</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4199</v>
+        <v>0.6728</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4782</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6367</v>
+        <v>-0.5184</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7953</v>
+        <v>-0.2638</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1586</v>
+        <v>-0.2545</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.1716</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7487</v>
+        <v>0.2478</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1036</v>
+        <v>-0.1936</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6451</v>
+        <v>0.4413</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4234</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2277</v>
+        <v>1.6181</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7942</v>
+        <v>4.0733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4334</v>
+        <v>-2.4552</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8374</v>
+        <v>0.551</v>
       </c>
       <c r="H5" t="n">
-        <v>0.409</v>
+        <v>-0.0861</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4285</v>
+        <v>0.6371</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3558</v>
+        <v>1.9328</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6728</v>
+        <v>1.3185</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6143</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5184</v>
+        <v>-1.3818</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2638</v>
+        <v>-1.4046</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2545</v>
+        <v>0.0228</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2045</v>
+        <v>0.4653</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5616</v>
+        <v>0.4002</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3571</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1911</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.9314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7208</v>
+        <v>1.0821</v>
       </c>
       <c r="E6" t="n">
-        <v>3.541</v>
+        <v>3.7522</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8202</v>
+        <v>-2.67</v>
       </c>
       <c r="G6" t="n">
-        <v>0.551</v>
+        <v>2.5559</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0861</v>
+        <v>-0.9375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6371</v>
+        <v>3.4934</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9328</v>
+        <v>4.9373</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3185</v>
+        <v>0.3972</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6143</v>
+        <v>4.5401</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3818</v>
+        <v>-2.3814</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4046</v>
+        <v>-1.3347</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0228</v>
+        <v>-1.0467</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.432</v>
+        <v>0.647</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.132</v>
+        <v>0.5305</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3</v>
+        <v>0.1164</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1911</v>
+        <v>-1.3278</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.9314</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3141</v>
+        <v>-0.3328</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6087</v>
+        <v>-1.0135</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9227</v>
+        <v>0.6807</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5559</v>
+        <v>0.305</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9375</v>
+        <v>0.6246</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4934</v>
+        <v>-0.3196</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9373</v>
+        <v>0.9417</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3972</v>
+        <v>1.4199</v>
       </c>
       <c r="L7" t="n">
-        <v>4.5401</v>
+        <v>-0.4782</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3814</v>
+        <v>-0.6367</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3347</v>
+        <v>-0.7953</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0467</v>
+        <v>0.1586</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7929</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7492</v>
+        <v>1.1104</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6129</v>
+        <v>0.8022</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1363</v>
+        <v>0.3082</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3278</v>
+        <v>1.4234</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5944</v>
+        <v>0.2163</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.339</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1227</v>
+        <v>1.655</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9659</v>
+        <v>-1.9939</v>
       </c>
       <c r="G8" t="n">
         <v>1.5266</v>
@@ -1078,13 +1078,13 @@
         <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1032</v>
+        <v>0.401</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8001</v>
+        <v>-0.2679</v>
       </c>
       <c r="U8" t="n">
-        <v>0.697</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4737</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5731</v>
+        <v>-3.8443</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3928</v>
+        <v>-2.636</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1803</v>
+        <v>-1.2084</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9498</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2309</v>
+        <v>-0.0404</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3047</v>
+        <v>0.0615</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.102</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0612</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3993</v>
+        <v>-4.5158</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3845</v>
+        <v>-5.2203</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9853</v>
+        <v>0.7045</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4463</v>
@@ -1312,13 +1312,13 @@
         <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2275</v>
+        <v>0.111</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8112</v>
+        <v>-0.6469</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0387</v>
+        <v>0.7579</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.864000000000001</v>
+        <v>-0.9279999999999995</v>
       </c>
       <c r="E12" t="n">
-        <v>6.5812</v>
+        <v>7.517100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.444999999999999</v>
+        <v>-8.444900000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.035500000000001</v>
+        <v>3.0355</v>
       </c>
       <c r="H12" t="n">
         <v>-4.4634</v>
@@ -1390,16 +1390,16 @@
         <v>8.92</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3315</v>
+        <v>5.2676</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6619</v>
+        <v>1.5977</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6696</v>
+        <v>3.669600000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.284200000000001</v>
+        <v>-3.2842</v>
       </c>
       <c r="W12" t="n">
         <v>4.2804</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7619</v>
+        <v>4.7854</v>
       </c>
       <c r="E13" t="n">
         <v>6.555</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7931</v>
+        <v>-1.7696</v>
       </c>
       <c r="G13" t="n">
         <v>2.1878</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9522</v>
+        <v>-0.9287</v>
       </c>
       <c r="T13" t="n">
         <v>-0.8184</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1338</v>
+        <v>-0.1103</v>
       </c>
       <c r="V13" t="n">
         <v>1.5441</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0787</v>
+        <v>3.046</v>
       </c>
       <c r="E14" t="n">
         <v>3.0404</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0383</v>
+        <v>0.0057</v>
       </c>
       <c r="G14" t="n">
         <v>3.0714</v>
@@ -1546,13 +1546,13 @@
         <v>2.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2702</v>
+        <v>-0.3029</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2348</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0354</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.674</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3785</v>
+        <v>1.4523</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5639</v>
+        <v>1.6658</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1854</v>
+        <v>-0.2135</v>
       </c>
       <c r="G16" t="n">
         <v>0.2674</v>
@@ -1702,13 +1702,13 @@
         <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2169</v>
+        <v>-0.1432</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1574</v>
+        <v>0.1294</v>
       </c>
       <c r="V16" t="n">
         <v>0.337</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7165</v>
+        <v>1.1345</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1594</v>
+        <v>0.465</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5571</v>
+        <v>0.6695</v>
       </c>
       <c r="G17" t="n">
         <v>0.2592</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7914</v>
+        <v>-0.3735</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6019</v>
+        <v>-0.2963</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1895</v>
+        <v>-0.0772</v>
       </c>
       <c r="V17" t="n">
         <v>-0.337</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1668</v>
+        <v>0.1949</v>
       </c>
       <c r="E18" t="n">
         <v>0.886</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7191</v>
+        <v>-0.6911</v>
       </c>
       <c r="G18" t="n">
         <v>1.0182</v>
@@ -1858,13 +1858,13 @@
         <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1795</v>
+        <v>-0.1514</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8701</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6667</v>
+        <v>-0.8143</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8082</v>
+        <v>1.6045</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.475</v>
+        <v>-2.4188</v>
       </c>
       <c r="G20" t="n">
         <v>1.0369</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4104</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0072</v>
+        <v>-0.211</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4031</v>
+        <v>-0.347</v>
       </c>
       <c r="V20" t="n">
         <v>-2.6808</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8848</v>
+        <v>-1.2127</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6224</v>
+        <v>-1.0298</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2625</v>
+        <v>-0.1828</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9277</v>
@@ -2092,13 +2092,13 @@
         <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2342</v>
+        <v>-0.0936</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.11</v>
+        <v>-0.5174</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3442</v>
+        <v>0.4239</v>
       </c>
       <c r="V21" t="n">
         <v>2.0068</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4493</v>
+        <v>-2.015</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6079</v>
+        <v>-2.506</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1586</v>
+        <v>0.491</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6112</v>
@@ -2170,13 +2170,13 @@
         <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6398</v>
+        <v>-0.2055</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6019</v>
+        <v>-0.5</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0379</v>
+        <v>0.2945</v>
       </c>
       <c r="V22" t="n">
         <v>1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6787</v>
+        <v>-2.4024</v>
       </c>
       <c r="E23" t="n">
         <v>-1.4267</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2519</v>
+        <v>-0.9757</v>
       </c>
       <c r="G23" t="n">
         <v>-4.243</v>
@@ -2248,13 +2248,13 @@
         <v>2.3787</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9599</v>
+        <v>-0.6837</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2348</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7252</v>
+        <v>-0.4489</v>
       </c>
       <c r="V23" t="n">
         <v>1.1367</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1055</v>
+        <v>-4.1721</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3214</v>
+        <v>-3.2195</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7841</v>
+        <v>-0.9526</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6409</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1454</v>
+        <v>-0.212</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.624</v>
+        <v>-0.5221</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4786</v>
+        <v>0.3101</v>
       </c>
       <c r="V24" t="n">
         <v>0.2666</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.863899999999999</v>
+        <v>2.543099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>8.4452</v>
+        <v>8.445399999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.581300000000001</v>
+        <v>-5.902100000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-3.035400000000001</v>
@@ -2404,13 +2404,13 @@
         <v>14.8667</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.3315</v>
+        <v>-3.6525</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.6698</v>
+        <v>-3.6697</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6618000000000001</v>
+        <v>0.01739999999999992</v>
       </c>
       <c r="V25" t="n">
         <v>3.2844</v>
